--- a/docs/design/ACSMS-SCR-004/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_JAマスタ明細検索画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-004/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_JAマスタ明細検索画面_V1.0.xlsx
@@ -1700,7 +1700,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2151,7 +2151,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2719,7 +2719,7 @@
       <c r="U14" s="11" t="n"/>
       <c r="V14" s="19" t="inlineStr">
         <is>
-          <t>関連データが存在するため削除できません。</t>
+          <t>関連データが存在するため処理を実行できません。</t>
         </is>
       </c>
       <c r="W14" s="10" t="n"/>
@@ -2966,7 +2966,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3401,7 +3401,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -4429,7 +4429,7 @@
       <c r="AE28" s="11" t="n"/>
       <c r="AF28" s="19" t="inlineStr">
         <is>
-          <t>ソート項目（m_jaテーブルのカラム名を指定。例: ja_code, ja_name, yubin_no, todofuken_name, tel, address, fax）</t>
+          <t>ソート項目（例: ja_code, ja_name, yubin_no, todofuken_name, tel, address, fax, updated_at）</t>
         </is>
       </c>
       <c r="AG28" s="10" t="n"/>
@@ -6175,7 +6175,7 @@
     <row r="82" ht="36" customHeight="1">
       <c r="D82" s="41" t="inlineStr">
         <is>
-          <t>sort_by：列挙型（ja_code, ja_name, yubin_no, todofuken_name, tel, address, fax）</t>
+          <t>sort_by：列挙型（ja_code, ja_name, yubin_no, todofuken_name, tel, address, fax, updated_at）</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
